--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -706,16 +706,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>2.7</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -888,16 +906,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-6.2</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -905,16 +941,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>3.282</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1056,16 +1110,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>64.90900000000001</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Jordan</t>
+          <t>Central Bank of Jordan (discount rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -660,11 +660,7 @@
           <t>Sep-26</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>policy discount rate</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,16 +685,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>2.7011</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -773,7 +787,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF Country Report</t>
+          <t>IMF Country Report / Ministry of Finance</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government debt</t>
+          <t>Central government gross debt</t>
         </is>
       </c>
     </row>
@@ -808,7 +822,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance (central government primary deficit)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -839,7 +853,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance (central government headline deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -986,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>end-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1001,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross FX reserves, +11.7% YTD</t>
+          <t>CBJ gross foreign exchange reserves (gold treatment not stated)</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1052,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>end-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Jordan</t>
+          <t>Central Bank of Jordan (prospective goods and services imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1160,7 +1174,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Finance / Cbonds</t>
+          <t>Ministry of Finance (sum of four listed USD Eurobonds: 1.0 + 1.25 + 0.7 + 1.0)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,11 +1182,7 @@
           <t>Sep-26</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>sum of listed USD bonds: 1.0 (2028), 1.25 (2030), 0.7 (2032), 1.0 (2047)</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1321,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF (4-year) + RSF</t>
+          <t>4-year Extended Fund Facility (SDR 926.37m) plus RSF</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1344,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1368,10 +1378,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>2028F</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1386,7 +1401,8 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1397,7 +1413,8 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1408,7 +1425,8 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1419,7 +1437,8 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1432,7 +1451,12 @@
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Dec-25</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1445,7 +1469,12 @@
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Dec-25</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1460,11 +1489,14 @@
         <v>83.59999999999999</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>IMF Country Report, Jun-26</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IMF Country Report / Ministry of Finance, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1509,8 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1488,7 +1521,8 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1499,7 +1533,8 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1510,7 +1545,8 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government gross debt</t>
+          <t>Central government debt</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBJ gross foreign exchange reserves (gold treatment not stated)</t>
+          <t>CBJ gross foreign exchange reserves (record high, +11.7% YTD); gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-year Extended Fund Facility (SDR 926.37m) plus RSF</t>
+          <t>Extended Fund Facility (4-year, SDR 926.37m) plus RSF; Fifth EFF Review completed Jun-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF Country Report / Ministry of Finance, Jun-26</t>
+          <t>IMF Country Report / Ministry of Finance, Jun-26 (2028F is the EFF target)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt</t>
+          <t>Central government gross debt</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dec-25</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dec-25</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBJ gross foreign exchange reserves (record high, +11.7% YTD); gold treatment not stated</t>
+          <t>CBJ gross foreign exchange reserves (record high, +11.7% YTD)</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year, SDR 926.37m) plus RSF; Fifth EFF Review completed Jun-26</t>
+          <t>Extended Fund Facility (4-year); Fifth Review completed Jun-26, plus RSF Second Review</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1454,7 +1454,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ministry of Finance, Dec-25</t>
+          <t>Ministry of Finance, 31-Dec-25</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ministry of Finance, Dec-25</t>
+          <t>Ministry of Finance, 31-Dec-25</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF Country Report / Ministry of Finance, Jun-26 (2028F is the EFF target)</t>
+          <t>IMF Country Report / Ministry of Finance, 30-Jun-26 (2026E and 2028F are projections/targets under the EFF)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBJ gross foreign exchange reserves (record high, +11.7% YTD)</t>
+          <t>CBJ gross foreign exchange reserves, record high</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year); Fifth Review completed Jun-26, plus RSF Second Review</t>
+          <t>Extended Fund Facility (4-year) plus RSF; Fifth EFF review completed Jun-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1454,7 +1454,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ministry of Finance, 31-Dec-25</t>
+          <t>Ministry of Finance, 31-Dec-25 (central government)</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ministry of Finance, 31-Dec-25</t>
+          <t>Ministry of Finance, 31-Dec-25 (central government)</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF Country Report / Ministry of Finance, 30-Jun-26 (2026E and 2028F are projections/targets under the EFF)</t>
+          <t>IMF Country Report / Ministry of Finance, 30-Jun-26 (central government; 2026E and 2028F are IMF EFF projections/targets)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government gross debt</t>
+          <t>Central government debt</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ministry of Finance (central government primary deficit)</t>
+          <t>Ministry of Finance (central government)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -853,12 +853,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance (central government headline deficit)</t>
+          <t>Ministry of Finance (central government)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBJ gross foreign exchange reserves, record high</t>
+          <t>CBJ gross foreign exchange reserves; gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Finance (sum of four listed USD Eurobonds: 1.0 + 1.25 + 0.7 + 1.0)</t>
+          <t>Ministry of Finance (sum of four USD Eurobonds: 1.0 + 1.25 + 0.7 + 1.0)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year) plus RSF; Fifth EFF review completed Jun-26</t>
+          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1454,7 +1454,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ministry of Finance, 31-Dec-25 (central government)</t>
+          <t>Ministry of Finance, Dec-25</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ministry of Finance, 31-Dec-25 (central government)</t>
+          <t>Ministry of Finance, Dec-25</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF Country Report / Ministry of Finance, 30-Jun-26 (central government; 2026E and 2028F are IMF EFF projections/targets)</t>
+          <t>IMF Country Report / Ministry of Finance, Jun-26 (2028F is the IMF EFF target)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt</t>
+          <t>Central government gross debt</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ministry of Finance (central government)</t>
+          <t>Ministry of Finance (central government primary deficit)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance (central government)</t>
+          <t>Ministry of Finance (headline deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBJ gross foreign exchange reserves; gold treatment not stated</t>
+          <t>CBJ gross foreign exchange reserves, record high (+11.7% YTD)</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year, SDR 926.37m; Fifth Review completed Jun-26, with RSF)</t>
+          <t>Extended Fund Facility (4-year), with RSF</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF Country Report / Ministry of Finance, Jun-26 (2028F is the IMF EFF target)</t>
+          <t>IMF Country Report / Ministry of Finance, Jun-26 (central government debt; 2028F is the EFF target)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government gross debt</t>
+          <t>Central government debt</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ministry of Finance (central government primary deficit)</t>
+          <t>Ministry of Finance (central government)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance (headline deficit)</t>
+          <t>Ministry of Finance (central government)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBJ gross foreign exchange reserves, record high (+11.7% YTD)</t>
+          <t>CBJ gross foreign exchange reserves, record high; +11.7% YTD</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (4-year), with RSF</t>
+          <t>Extended Fund Facility (4-year, plus RSF)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF Country Report / Ministry of Finance, Jun-26 (central government debt; 2028F is the EFF target)</t>
+          <t>IMF Country Report / Ministry of Finance, Jun-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Jordan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Jordan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/jordan.json</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
